--- a/analysis/supplementary-materials/S3_Table.xlsx
+++ b/analysis/supplementary-materials/S3_Table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -32,6 +32,12 @@
     <t xml:space="preserve">Bayes_p</t>
   </si>
   <si>
+    <t xml:space="preserve">CI_lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI_hi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ae.ae abundance ~ surveillance strategy (Eq. 1,2)</t>
   </si>
   <si>
@@ -45,6 +51,9 @@
   </si>
   <si>
     <t xml:space="preserve">Variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayes_Rsquared</t>
   </si>
   <si>
     <t xml:space="preserve">Any DENV+ Ae.ae ~ surveillance strategy (Eq. 3,4)</t>
@@ -413,210 +422,236 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
         <v>6720</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>0.52663690476193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.521951339285714</v>
+        <v>0.52260625</v>
       </c>
       <c r="F2" t="n">
-        <v>0.407</v>
-      </c>
+        <v>0.427</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
         <v>6720</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>0.76889880952381</v>
       </c>
       <c r="E3" t="n">
-        <v>0.77268869047619</v>
+        <v>0.772386904761905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.723</v>
-      </c>
+        <v>0.692</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="n">
         <v>6720</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>127</v>
       </c>
       <c r="E4" t="n">
-        <v>29.996</v>
+        <v>30.485</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
         <v>6720</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>5.39801041733174</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2145797828785</v>
+        <v>2.22423373987413</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>6720</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.0602409638554216</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D6"/>
       <c r="E6" t="n">
-        <v>0.0629132530120482</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.608</v>
+        <v>0.0221759411656095</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6" t="n">
+        <v>0.0148476531913025</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0321231794531882</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" t="n">
         <v>1245</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.939759036144578</v>
+        <v>0.0602409638554216</v>
       </c>
       <c r="E7" t="n">
-        <v>0.937086746987952</v>
+        <v>0.0627734939759036</v>
       </c>
       <c r="F7" t="n">
-        <v>0.42</v>
-      </c>
+        <v>0.597</v>
+      </c>
+      <c r="G7"/>
+      <c r="H7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" t="n">
         <v>1245</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.939759036144578</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.937226506024096</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
+        <v>0.435</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="n">
-        <v>1245</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
       <c r="D9" t="n">
-        <v>0.0566574981598434</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0589066400650834</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.58</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G9"/>
+      <c r="H9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="n">
-        <v>1245</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
       <c r="D10" t="n">
-        <v>0.0602409638554216</v>
+        <v>0.0566574981598434</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0639815261044177</v>
+        <v>0.0587853381371143</v>
       </c>
       <c r="F10" t="n">
-        <v>0.645</v>
-      </c>
+        <v>0.565</v>
+      </c>
+      <c r="G10"/>
+      <c r="H10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
         <v>1245</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.939759036144578</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D11"/>
       <c r="E11" t="n">
-        <v>0.936018473895582</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.392</v>
+        <v>0.039724491502926</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11" t="n">
+        <v>0.0131442760798239</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0790896047793631</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
         <v>1245</v>
@@ -625,18 +660,20 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.0602409638554216</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.0637935742971888</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
+        <v>0.649</v>
+      </c>
+      <c r="G12"/>
+      <c r="H12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n">
         <v>1245</v>
@@ -645,378 +682,416 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0566574981598434</v>
+        <v>0.939759036144578</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0598390810831751</v>
+        <v>0.936206425702811</v>
       </c>
       <c r="F13" t="n">
-        <v>0.608</v>
-      </c>
+        <v>0.391</v>
+      </c>
+      <c r="G13"/>
+      <c r="H13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="n">
         <v>1245</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0602409638554216</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0608128514056225</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.516</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G14"/>
+      <c r="H14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" t="n">
         <v>1245</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>0.939759036144578</v>
+        <v>0.0566574981598434</v>
       </c>
       <c r="E15" t="n">
-        <v>0.939187148594377</v>
+        <v>0.0596753147638786</v>
       </c>
       <c r="F15" t="n">
-        <v>0.518</v>
-      </c>
+        <v>0.609</v>
+      </c>
+      <c r="G15"/>
+      <c r="H15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1245</v>
+      </c>
+      <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="n">
-        <v>1245</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
+      <c r="D16"/>
       <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
+        <v>0.0737932462911149</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16" t="n">
+        <v>0.0361656671866948</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.119166985330661</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B17" t="n">
         <v>1245</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0566574981598434</v>
+        <v>0.0602409638554216</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0570788401193197</v>
+        <v>0.0602506024096386</v>
       </c>
       <c r="F17" t="n">
-        <v>0.497</v>
-      </c>
+        <v>0.496</v>
+      </c>
+      <c r="G17"/>
+      <c r="H17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>31</v>
+        <v>1245</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>3.03225806451613</v>
+        <v>0.939759036144578</v>
       </c>
       <c r="E18" t="n">
-        <v>3.06029032258065</v>
+        <v>0.939749397590361</v>
       </c>
       <c r="F18" t="n">
-        <v>0.506</v>
-      </c>
+        <v>0.543</v>
+      </c>
+      <c r="G18"/>
+      <c r="H18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>1245</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>0.645161290322581</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.439032258064516</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.002</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G19"/>
+      <c r="H19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>1245</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>0.0566574981598434</v>
       </c>
       <c r="E20" t="n">
-        <v>45.836</v>
+        <v>0.0565806505765828</v>
       </c>
       <c r="F20" t="n">
-        <v>0.284</v>
-      </c>
+        <v>0.475</v>
+      </c>
+      <c r="G20"/>
+      <c r="H20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B21" t="n">
-        <v>31</v>
+        <v>1245</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="n">
-        <v>89.6989247311828</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D21"/>
       <c r="E21" t="n">
-        <v>71.5215612903226</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.215</v>
+        <v>0.0970272178305889</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" t="n">
+        <v>0.0605799900284436</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.139194390625756</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>6.95652173913044</v>
+        <v>3.03225806451613</v>
       </c>
       <c r="E22" t="n">
-        <v>8.06195652173913</v>
+        <v>3.1009435483871</v>
       </c>
       <c r="F22" t="n">
-        <v>0.912</v>
-      </c>
+        <v>0.541</v>
+      </c>
+      <c r="G22"/>
+      <c r="H22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.645161290322581</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00291304347826087</v>
+        <v>0.432370967741936</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="G23"/>
+      <c r="H23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
-        <v>19.885</v>
+        <v>46.07275</v>
       </c>
       <c r="F24" t="n">
-        <v>0.248</v>
-      </c>
+        <v>0.296</v>
+      </c>
+      <c r="G24"/>
+      <c r="H24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B25" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>40.6798418972332</v>
+        <v>89.6989247311828</v>
       </c>
       <c r="E25" t="n">
-        <v>21.4034743083004</v>
+        <v>72.393688172043</v>
       </c>
       <c r="F25" t="n">
-        <v>0.033</v>
-      </c>
+        <v>0.226</v>
+      </c>
+      <c r="G25"/>
+      <c r="H25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" t="n">
-        <v>6.95652173913044</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D26"/>
       <c r="E26" t="n">
-        <v>7.0704347826087</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.539</v>
+        <v>0.877807478981571</v>
+      </c>
+      <c r="F26"/>
+      <c r="G26" t="n">
+        <v>0.726283701331334</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.932103739074894</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B27" t="n">
         <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>6.95652173913044</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00226086956521739</v>
+        <v>8.12590217391304</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
+        <v>0.921</v>
+      </c>
+      <c r="G27"/>
+      <c r="H27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B28" t="n">
         <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>14.315</v>
+        <v>0.00289130434782609</v>
       </c>
       <c r="F28" t="n">
-        <v>0.014</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G28"/>
+      <c r="H28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B29" t="n">
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>40.6798418972332</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
-        <v>10.2682964426877</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
-      </c>
+        <v>0.252</v>
+      </c>
+      <c r="G29"/>
+      <c r="H29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B30" t="n">
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>6.95652173913044</v>
+        <v>40.6798418972332</v>
       </c>
       <c r="E30" t="n">
-        <v>8.01917391304348</v>
+        <v>21.6956363636364</v>
       </c>
       <c r="F30" t="n">
-        <v>0.902</v>
-      </c>
+        <v>0.035</v>
+      </c>
+      <c r="G30"/>
+      <c r="H30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B31" t="n">
         <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D31"/>
       <c r="E31" t="n">
-        <v>0.00130434782608695</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
+        <v>0.421629992724071</v>
+      </c>
+      <c r="F31"/>
+      <c r="G31" t="n">
+        <v>0.166277192356496</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.63651706200376</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B32" t="n">
         <v>23</v>
@@ -1025,18 +1100,20 @@
         <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>23</v>
+        <v>6.95652173913044</v>
       </c>
       <c r="E32" t="n">
-        <v>16.311</v>
+        <v>7.07802173913043</v>
       </c>
       <c r="F32" t="n">
-        <v>0.064</v>
-      </c>
+        <v>0.548</v>
+      </c>
+      <c r="G32"/>
+      <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B33" t="n">
         <v>23</v>
@@ -1045,13 +1122,191 @@
         <v>10</v>
       </c>
       <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.00243478260869565</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33"/>
+      <c r="H33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>23</v>
+      </c>
+      <c r="E34" t="n">
+        <v>14.3065</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G34"/>
+      <c r="H34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="n">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="n">
         <v>40.6798418972332</v>
       </c>
-      <c r="E33" t="n">
-        <v>12.5399169960474</v>
-      </c>
-      <c r="F33" t="n">
+      <c r="E35" t="n">
+        <v>10.2597173913043</v>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
+      </c>
+      <c r="G35"/>
+      <c r="H35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36"/>
+      <c r="E36" t="n">
+        <v>0.0824340964608231</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36" t="n">
+        <v>0.0206034864394323</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.199515612109104</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6.95652173913044</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8.09163043478261</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="G37"/>
+      <c r="H37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="n">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.00113043478260869</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38"/>
+      <c r="H38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" t="n">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.415</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" t="n">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>40.6798418972332</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12.8464841897233</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="n">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41"/>
+      <c r="E41" t="n">
+        <v>0.132453335094479</v>
+      </c>
+      <c r="F41"/>
+      <c r="G41" t="n">
+        <v>0.0299258010701777</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.298192601722788</v>
       </c>
     </row>
   </sheetData>
